--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -25,13 +25,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/VFImmunizationReaction</t>
+    <t>http://va.gov/fhir/ConceptMap/CMVFImmunizationReaction</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,7 +94,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFImmunizationReaction</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFImmunizationReaction</t>
   </si>
   <si>
     <t>Display</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -46,7 +46,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="74">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
   <si>
     <t>NONE</t>
@@ -775,16 +772,16 @@
         <v>71</v>
       </c>
       <c r="B3" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
+      <c r="E3" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="75">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t>NONE</t>
@@ -772,16 +775,16 @@
         <v>71</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s" s="2">
         <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -52,13 +52,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,6 +94,12 @@
     <t>Source</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFImmunizationReaction-vista</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFImmunizationReaction</t>
   </si>
   <si>
@@ -101,9 +107,6 @@
   </si>
   <si>
     <t>Relationship</t>
-  </si>
-  <si>
-    <t>Target</t>
   </si>
   <si>
     <t>http://va.gov/terminology/vistaDefinedElements/9000010.11-.06</t>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -493,6 +496,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -510,220 +521,220 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>29</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -741,50 +752,50 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>29</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -70,7 +70,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFImmunizationReaction.xlsx
+++ b/docs/CMVFImmunizationReaction.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
